--- a/product_upload/packages/4/file.xlsx
+++ b/product_upload/packages/4/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR101"/>
+  <dimension ref="A1:AS101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -639,6 +639,11 @@
         </is>
       </c>
       <c r="AR1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -667,7 +672,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -814,6 +819,11 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>LORINEX 5MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>SKU-485C8DCB921A</t>
         </is>
       </c>
@@ -841,7 +851,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -996,6 +1006,11 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>LORVAST 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>SKU-681991D885B4</t>
         </is>
       </c>
@@ -1023,7 +1038,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1174,6 +1189,11 @@
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>LORVAST 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>SKU-072D6BCB5FED</t>
         </is>
       </c>
@@ -1201,7 +1221,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1352,6 +1372,11 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>LORVAST 40 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>SKU-4AF238F2335C</t>
         </is>
       </c>
@@ -1379,7 +1404,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1532,6 +1557,11 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>LOXTRA EYE DROP</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>SKU-CF2352F22C8F</t>
         </is>
       </c>
@@ -1559,7 +1589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1710,6 +1740,11 @@
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>LOXOL 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>SKU-61C8B570F60B</t>
         </is>
       </c>
@@ -1737,7 +1772,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1892,6 +1927,11 @@
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>LOXOL 25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>SKU-7700CCED4A18</t>
         </is>
       </c>
@@ -1919,7 +1959,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2074,6 +2114,11 @@
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>LOXOL 200MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>SKU-48D6DEFD5AA3</t>
         </is>
       </c>
@@ -2101,7 +2146,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2260,6 +2305,11 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>LOXOL 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>SKU-2D0C04B96904</t>
         </is>
       </c>
@@ -2287,7 +2337,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2438,6 +2488,11 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>LOWVASC 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>SKU-3106D045CA23</t>
         </is>
       </c>
@@ -2465,7 +2520,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2616,6 +2671,11 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>LOWRAC 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>SKU-871E24AD63FB</t>
         </is>
       </c>
@@ -2643,7 +2703,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2800,6 +2860,11 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>LOTEVAN 5/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
           <t>SKU-8416B16DD1E9</t>
         </is>
       </c>
@@ -2827,7 +2892,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2988,6 +3053,11 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>LOTEVAN 10/320MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>SKU-5878EC939844</t>
         </is>
       </c>
@@ -3015,7 +3085,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3176,6 +3246,11 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>LOTEVAN 10/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>SKU-625001153069</t>
         </is>
       </c>
@@ -3203,7 +3278,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3362,6 +3437,11 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>LOTENSE 5MG CAP</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>SKU-BB50F1374A3A</t>
         </is>
       </c>
@@ -3389,7 +3469,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3548,6 +3628,11 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>LOTENSE 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>SKU-998F6E0BBBC3</t>
         </is>
       </c>
@@ -3575,7 +3660,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3722,6 +3807,11 @@
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>LOSEC MUPS 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>SKU-6F0F4A308C3A</t>
         </is>
       </c>
@@ -3749,7 +3839,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3904,6 +3994,11 @@
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>LOSEC MUPS 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>SKU-ECA458785469</t>
         </is>
       </c>
@@ -3931,7 +4026,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4084,6 +4179,11 @@
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>LOTEVAN 5/320MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>SKU-FE655B9F2839</t>
         </is>
       </c>
@@ -4111,7 +4211,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4272,6 +4372,11 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>MEGAMOX 625 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>SKU-26DB85D6FB34</t>
         </is>
       </c>
@@ -4299,7 +4404,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4460,6 +4565,11 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>MEGAMOX 625 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>SKU-6D0244738660</t>
         </is>
       </c>
@@ -4487,7 +4597,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4640,6 +4750,11 @@
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>MEGAMOX 457MG SUSP</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>SKU-539770C2F0D2</t>
         </is>
       </c>
@@ -4667,7 +4782,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4824,6 +4939,11 @@
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>MEGAMOX 312MG SUSP</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>SKU-109374C4F28F</t>
         </is>
       </c>
@@ -4851,7 +4971,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5012,6 +5132,11 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>MEGAMOX 228 MG SUSP</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>SKU-B6A5D42C7CA7</t>
         </is>
       </c>
@@ -5039,7 +5164,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5192,6 +5317,11 @@
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr">
         <is>
+          <t>MEGAMOX 1GM TAB</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>SKU-170735D0D9D3</t>
         </is>
       </c>
@@ -5219,7 +5349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5376,6 +5506,11 @@
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>MEGAMOX 156 MG SUSP</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>SKU-6BDC65FC862E</t>
         </is>
       </c>
@@ -5403,7 +5538,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5558,6 +5693,11 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
+          <t>MEGACE</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
           <t>SKU-62310D531ED2</t>
         </is>
       </c>
@@ -5585,7 +5725,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5736,6 +5876,11 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>MEGACE</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>SKU-64FA1D209F90</t>
         </is>
       </c>
@@ -5763,7 +5908,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5914,6 +6059,11 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
+          <t>ZOYLEX  5% CREAM</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
           <t>SKU-8B24BF59E1D5</t>
         </is>
       </c>
@@ -5941,7 +6091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6088,6 +6238,11 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
         <is>
+          <t>MEIACT 200 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>SKU-62B18BEDC6BA</t>
         </is>
       </c>
@@ -6115,7 +6270,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6266,6 +6421,11 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
+          <t>MEPICATON 3% CARTRIDGES (1.8)ML</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
           <t>SKU-1780B4083C90</t>
         </is>
       </c>
@@ -6293,7 +6453,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6452,6 +6612,11 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>MEPHAQUIN LACTAB</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
           <t>SKU-5FC1FDA3EE9F</t>
         </is>
       </c>
@@ -6479,7 +6644,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6636,6 +6801,11 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>MENTEX SYRUP</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>SKU-5E2280377DCE</t>
         </is>
       </c>
@@ -6663,7 +6833,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6822,6 +6992,11 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
+          <t>MENACTRA 4 MCG SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
           <t>SKU-5171F21D14A0</t>
         </is>
       </c>
@@ -6849,7 +7024,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7012,6 +7187,11 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>MENACTRA</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
           <t>SKU-CD9657F6C4CC</t>
         </is>
       </c>
@@ -7039,7 +7219,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7194,6 +7374,11 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
         <is>
+          <t>MEDROL 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
           <t>SKU-2FD8FC2E8AAD</t>
         </is>
       </c>
@@ -7221,7 +7406,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7370,6 +7555,11 @@
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr">
         <is>
+          <t>MEDICAINE 2% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
           <t>SKU-EC7CC4832C3C</t>
         </is>
       </c>
@@ -7397,7 +7587,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7554,6 +7744,11 @@
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr">
         <is>
+          <t>MARVELON TAB</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
           <t>SKU-4730FE216AE2</t>
         </is>
       </c>
@@ -7581,7 +7776,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7736,6 +7931,11 @@
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr">
         <is>
+          <t>MAXIM 400MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
           <t>SKU-F2B73B2A15B5</t>
         </is>
       </c>
@@ -7763,7 +7963,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7918,6 +8118,11 @@
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr">
         <is>
+          <t>MAXIM 400MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
           <t>SKU-E1AED4EFE5B0</t>
         </is>
       </c>
@@ -7945,7 +8150,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8104,6 +8309,11 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
+          <t>MEBAGEN</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
           <t>SKU-DF230CC59C1D</t>
         </is>
       </c>
@@ -8131,7 +8341,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8282,6 +8492,11 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
+          <t>MEDEMYCIN</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
           <t>SKU-5D262946F34F</t>
         </is>
       </c>
@@ -8309,7 +8524,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8464,6 +8679,11 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
+          <t>MEDAFEN 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
           <t>SKU-2B3BB46B6D10</t>
         </is>
       </c>
@@ -8491,7 +8711,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8654,6 +8874,11 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
+          <t>MEDACIN -T 1% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
           <t>SKU-BDFBB24DF9FD</t>
         </is>
       </c>
@@ -8681,7 +8906,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8828,6 +9053,11 @@
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr">
         <is>
+          <t>MEDICAINE 3% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
           <t>SKU-19BB0045145F</t>
         </is>
       </c>
@@ -8855,7 +9085,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9006,6 +9236,11 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
         <is>
+          <t>MEDACIN -T 1% GEL</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
           <t>SKU-444CE0B431D4</t>
         </is>
       </c>
@@ -9033,7 +9268,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9184,6 +9419,11 @@
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr">
         <is>
+          <t>MEDACEF 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
           <t>SKU-A3DE1AE18296</t>
         </is>
       </c>
@@ -9211,7 +9451,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9362,6 +9602,11 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>MEDACEF 250MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
           <t>SKU-26D72F894C39</t>
         </is>
       </c>
@@ -9389,7 +9634,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9536,6 +9781,11 @@
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>LOPRAM 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
           <t>SKU-773AC1727B5F</t>
         </is>
       </c>
@@ -9563,7 +9813,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9722,6 +9972,11 @@
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr">
         <is>
+          <t>LOPID</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>SKU-49D29F8CE860</t>
         </is>
       </c>
@@ -9749,7 +10004,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9908,6 +10163,11 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
+          <t>LEJAM 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
           <t>SKU-654C4C9A8C5D</t>
         </is>
       </c>
@@ -9935,7 +10195,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10090,6 +10350,11 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
         <is>
+          <t>LEDO 5% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
           <t>SKU-2E5874A3F3E2</t>
         </is>
       </c>
@@ -10117,7 +10382,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10268,6 +10533,11 @@
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="inlineStr">
         <is>
+          <t>LECITAL 20MG F.C. CAPLETS</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
           <t>SKU-71DDBC87FF12</t>
         </is>
       </c>
@@ -10295,7 +10565,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10442,6 +10712,11 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr">
         <is>
+          <t>LAXOLAC SYRUP</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
           <t>SKU-8181FCE30E9C</t>
         </is>
       </c>
@@ -10469,7 +10744,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10620,6 +10895,11 @@
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>LAXOLAC SYRUP</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
           <t>SKU-713C60497809</t>
         </is>
       </c>
@@ -10647,7 +10927,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10796,6 +11076,11 @@
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>LAXO</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
           <t>SKU-D47BED2A27A0</t>
         </is>
       </c>
@@ -10823,7 +11108,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10984,6 +11269,11 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>LATANOCOM OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
           <t>SKU-EDC591F8C581</t>
         </is>
       </c>
@@ -11011,7 +11301,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11166,6 +11456,11 @@
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr">
         <is>
+          <t>LATANO 0.005% W-V OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
           <t>SKU-40D0C86DC49C</t>
         </is>
       </c>
@@ -11193,7 +11488,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11344,6 +11639,11 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
+          <t>LASONIL OINT</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>SKU-B23A017BBE8A</t>
         </is>
       </c>
@@ -11371,7 +11671,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11530,6 +11830,11 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
+          <t>LEJAM 60MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
           <t>SKU-EEEB212DA585</t>
         </is>
       </c>
@@ -11557,7 +11862,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11708,6 +12013,11 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
+          <t>LENDOMAX 70 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
           <t>SKU-828479E8CF90</t>
         </is>
       </c>
@@ -11735,7 +12045,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11892,6 +12202,11 @@
       <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="inlineStr">
         <is>
+          <t>LERCADIP 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
           <t>SKU-2F359D6A06C6</t>
         </is>
       </c>
@@ -11919,7 +12234,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12062,6 +12377,11 @@
       <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr">
         <is>
+          <t>LEVSIN TAB 0.125MG</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
           <t>SKU-A2C7C8F3CEFB</t>
         </is>
       </c>
@@ -12089,7 +12409,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12244,6 +12564,11 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr">
         <is>
+          <t>LEVOZAL 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
           <t>SKU-60A489EDAB2E</t>
         </is>
       </c>
@@ -12271,7 +12596,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12428,6 +12753,11 @@
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="inlineStr">
         <is>
+          <t>LEVOX 750MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
           <t>SKU-B829C90A173B</t>
         </is>
       </c>
@@ -12455,7 +12785,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12612,6 +12942,11 @@
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr">
         <is>
+          <t>LEVOX 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
           <t>SKU-D6AE96AB4938</t>
         </is>
       </c>
@@ -12639,7 +12974,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12794,6 +13129,11 @@
       <c r="AQ68" t="inlineStr"/>
       <c r="AR68" t="inlineStr">
         <is>
+          <t>LASIX TAB 40 MG</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
           <t>SKU-C505F5120921</t>
         </is>
       </c>
@@ -12821,7 +13161,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12980,6 +13320,11 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
+          <t>LEVONIC 500MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
           <t>SKU-DCF7B7EACA9B</t>
         </is>
       </c>
@@ -13007,7 +13352,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13154,6 +13499,11 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr">
         <is>
+          <t>LEVITRA 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
           <t>SKU-4B27E921F187</t>
         </is>
       </c>
@@ -13181,7 +13531,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13328,6 +13678,11 @@
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr">
         <is>
+          <t>LEVITRA 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
           <t>SKU-14D1106A6F1F</t>
         </is>
       </c>
@@ -13355,7 +13710,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13508,6 +13863,11 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
+          <t>LEVITRA 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
           <t>SKU-03A1266743ED</t>
         </is>
       </c>
@@ -13535,7 +13895,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13704,6 +14064,11 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
+          <t>LEVEMIR FLEX PEN 100IU\ML</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
           <t>SKU-83A3AE635200</t>
         </is>
       </c>
@@ -13731,7 +14096,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13882,6 +14247,11 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
+          <t>LEUKAST 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
           <t>SKU-C744B347469E</t>
         </is>
       </c>
@@ -13909,7 +14279,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14072,6 +14442,11 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
+          <t>LEVOFLOX 500MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
           <t>SKU-9FC640BF915B</t>
         </is>
       </c>
@@ -14099,7 +14474,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14250,6 +14625,11 @@
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr">
         <is>
+          <t>LAMISIL ONCE 1% CUTANEOUS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
           <t>SKU-E92EB6DD602D</t>
         </is>
       </c>
@@ -14277,7 +14657,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14438,6 +14818,11 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
+          <t>LAMISIL 250 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
           <t>SKU-705232EC7CCE</t>
         </is>
       </c>
@@ -14465,7 +14850,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14624,6 +15009,11 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr">
         <is>
+          <t>LAMISIL 1% SPRAY</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
           <t>SKU-F3644F9C36DD</t>
         </is>
       </c>
@@ -14651,7 +15041,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14810,6 +15200,11 @@
       <c r="AQ79" t="inlineStr"/>
       <c r="AR79" t="inlineStr">
         <is>
+          <t>LAMISIL 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
           <t>SKU-7DE00C67E5BC</t>
         </is>
       </c>
@@ -14837,7 +15232,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14988,6 +15383,11 @@
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
         <is>
+          <t>LAMIFEN 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
           <t>SKU-FEE16DFC9F9B</t>
         </is>
       </c>
@@ -15015,7 +15415,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15174,6 +15574,11 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
+          <t>LAMIFEN 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
           <t>SKU-7D2A918C0755</t>
         </is>
       </c>
@@ -15201,7 +15606,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15352,6 +15757,11 @@
       <c r="AQ82" t="inlineStr"/>
       <c r="AR82" t="inlineStr">
         <is>
+          <t>LAMIFEN 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
           <t>SKU-6FAD258C067A</t>
         </is>
       </c>
@@ -15379,7 +15789,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15534,6 +15944,11 @@
       <c r="AQ83" t="inlineStr"/>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
           <t>SKU-BE6AEF458C34</t>
         </is>
       </c>
@@ -15561,7 +15976,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15720,6 +16135,11 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
           <t>SKU-B4F2FD31D0EE</t>
         </is>
       </c>
@@ -15747,7 +16167,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15906,6 +16326,11 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
           <t>SKU-97BFC5788C74</t>
         </is>
       </c>
@@ -15933,7 +16358,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16092,6 +16517,11 @@
       </c>
       <c r="AR86" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
           <t>SKU-B6ABD96FB94F</t>
         </is>
       </c>
@@ -16119,7 +16549,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16274,6 +16704,11 @@
       <c r="AQ87" t="inlineStr"/>
       <c r="AR87" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
           <t>SKU-6C0CA7AE0751</t>
         </is>
       </c>
@@ -16301,7 +16736,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16452,6 +16887,11 @@
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
           <t>SKU-59EB9F07C31F</t>
         </is>
       </c>
@@ -16479,7 +16919,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16630,6 +17070,11 @@
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr">
         <is>
+          <t>LAMOTRIX 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
           <t>SKU-E05C0F9FDF52</t>
         </is>
       </c>
@@ -16657,7 +17102,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16808,6 +17253,11 @@
       <c r="AQ90" t="inlineStr"/>
       <c r="AR90" t="inlineStr">
         <is>
+          <t>LAMOTRIX 25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
           <t>SKU-5ED029114247</t>
         </is>
       </c>
@@ -16835,7 +17285,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16990,6 +17440,11 @@
       </c>
       <c r="AR91" t="inlineStr">
         <is>
+          <t>LAMOTRIX 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
           <t>SKU-355C562A6720</t>
         </is>
       </c>
@@ -17017,7 +17472,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17168,6 +17623,11 @@
       <c r="AQ92" t="inlineStr"/>
       <c r="AR92" t="inlineStr">
         <is>
+          <t>LAPRIL 5 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
           <t>SKU-3142B0460601</t>
         </is>
       </c>
@@ -17195,7 +17655,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17346,6 +17806,11 @@
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="inlineStr">
         <is>
+          <t>LAPRIL 20MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
           <t>SKU-FC6F07263771</t>
         </is>
       </c>
@@ -17373,7 +17838,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17524,6 +17989,11 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
+          <t>LAPRIL 20 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
           <t>SKU-FCDE5734B076</t>
         </is>
       </c>
@@ -17551,7 +18021,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17706,6 +18176,11 @@
       <c r="AQ95" t="inlineStr"/>
       <c r="AR95" t="inlineStr">
         <is>
+          <t>LAPRIL 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
           <t>SKU-7AB7177A1F6E</t>
         </is>
       </c>
@@ -17733,7 +18208,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17888,6 +18363,11 @@
       <c r="AQ96" t="inlineStr"/>
       <c r="AR96" t="inlineStr">
         <is>
+          <t>LAPRIX 5MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
           <t>SKU-40BB10E4426D</t>
         </is>
       </c>
@@ -17915,7 +18395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18070,6 +18550,11 @@
       <c r="AQ97" t="inlineStr"/>
       <c r="AR97" t="inlineStr">
         <is>
+          <t>LAPRIX 10MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
           <t>SKU-D141C875A7A8</t>
         </is>
       </c>
@@ -18097,7 +18582,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18254,6 +18739,11 @@
       </c>
       <c r="AR98" t="inlineStr">
         <is>
+          <t>LANTUS 100 I.U - ML VIAL</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
           <t>SKU-659ADF985C1F</t>
         </is>
       </c>
@@ -18281,7 +18771,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18436,6 +18926,11 @@
       </c>
       <c r="AR99" t="inlineStr">
         <is>
+          <t>LANSOMID 30 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
           <t>SKU-4B45B26C7DBB</t>
         </is>
       </c>
@@ -18463,7 +18958,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18624,6 +19119,11 @@
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
         <is>
+          <t>LANTUS SOLOSTAR 100I.U-ML DISPOSABLE PEN</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
           <t>SKU-B3C156F9FF8E</t>
         </is>
       </c>
@@ -18651,7 +19151,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18801,6 +19301,11 @@
       <c r="AP101" t="inlineStr"/>
       <c r="AQ101" t="inlineStr"/>
       <c r="AR101" t="inlineStr">
+        <is>
+          <t>LIVOSTIN NASAL SPRAY 0.5MG-ML</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SKU-0EF17EDA9F4B</t>
         </is>
@@ -18817,7 +19322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18863,100 +19368,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18988,7 +19498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19003,92 +19513,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-49877</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>164.87</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>352</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19120,7 +19635,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19135,92 +19650,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-30995</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>427.98</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>353</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19252,7 +19772,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19267,92 +19787,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-58710</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>154.14</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>354</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19384,7 +19909,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19399,92 +19924,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-58457</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>451.87</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>355</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19516,7 +20046,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19531,92 +20061,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-31102</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>89.55</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>356</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19648,7 +20183,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19663,92 +20198,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-95690</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>456.19</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>357</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19780,7 +20320,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19795,92 +20335,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-75496</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>212.89</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>358</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19912,7 +20457,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19927,92 +20472,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-80082</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>236.73</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>359</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20044,7 +20594,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20059,92 +20609,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-70210</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>18.87</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>360</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20176,7 +20731,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20191,92 +20746,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-53741</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>337.42</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>361</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20308,7 +20868,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20323,92 +20883,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-10009</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>163.05</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>362</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20440,7 +21005,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20455,92 +21020,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-97553</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>29.19</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>363</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20557,7 +21127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20663,6 +21233,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20698,7 +21278,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20763,6 +21343,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-3F7D1F1D7114</t>
         </is>
@@ -20799,7 +21389,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20864,6 +21454,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-00F35A0B7D76</t>
         </is>
@@ -20900,7 +21500,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20965,6 +21565,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-F1A1352812E2</t>
         </is>
@@ -21001,7 +21611,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21066,6 +21676,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-244670323B03</t>
         </is>
@@ -21102,7 +21722,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21167,6 +21787,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-FF9A8AEF52B5</t>
         </is>
@@ -21203,7 +21833,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21268,6 +21898,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-57F3C1828F9D</t>
         </is>
@@ -21304,7 +21944,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21369,6 +22009,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-F9F2683E7EF1</t>
         </is>
@@ -21405,7 +22055,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21470,6 +22120,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-84DF185E6DC9</t>
         </is>
@@ -21506,7 +22166,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21571,6 +22231,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-425FA6D90F49</t>
         </is>
@@ -21607,7 +22277,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21672,6 +22342,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-DDF5EF51C975</t>
         </is>
@@ -21708,7 +22388,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21773,6 +22453,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-9FD4932C4772</t>
         </is>
@@ -21809,7 +22499,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21874,6 +22564,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-659325A6836A</t>
         </is>
@@ -21910,7 +22610,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21975,6 +22675,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-3D3B7B19BF65</t>
         </is>
@@ -22011,7 +22721,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22076,6 +22786,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-06120EEE4392</t>
         </is>
@@ -22112,7 +22832,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22177,6 +22897,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-F576F6E6139F</t>
         </is>
@@ -22213,7 +22943,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22278,6 +23008,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-7A99AF0205EC</t>
         </is>
@@ -22314,7 +23054,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22379,6 +23119,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-D62D199D668C</t>
         </is>
@@ -22415,7 +23165,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22480,6 +23230,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-EC0A541A81CC</t>
         </is>
@@ -22516,7 +23276,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22581,6 +23341,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-01130A522299</t>
         </is>
@@ -22617,7 +23387,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22682,6 +23452,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-71CC18CFE1F3</t>
         </is>

--- a/product_upload/packages/4/file.xlsx
+++ b/product_upload/packages/4/file.xlsx
@@ -680,8 +680,16 @@
           <t>3553722205-391-040550821239</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LORINEX 5MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -2345,8 +2353,16 @@
           <t>5521713867-260-049520225075</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LOWVASC 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2528,8 +2544,16 @@
           <t>8624713723-559-613565775159</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LOWRAC 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3668,8 +3692,16 @@
           <t>3474243796-070-514395239625</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LOSEC MUPS 20MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -5546,8 +5578,16 @@
           <t>8472800855-660-879513522405</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>MEGACE detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5733,8 +5773,16 @@
           <t>8621518182-793-859418308716</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>MEGACE detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5916,8 +5964,16 @@
           <t>2903719019-968-597604498998</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ZOYLEX  5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6099,8 +6155,16 @@
           <t>9776663430-600-623265878753</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>MEIACT 200 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6278,8 +6342,16 @@
           <t>2411673962-886-480380321345</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MEPICATON 3% CARTRIDGES (1.8)ML detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6841,8 +6913,16 @@
           <t>0393500873-868-890812522002</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MENACTRA 4 MCG SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -7414,8 +7494,16 @@
           <t>0780434960-585-780048778761</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>MEDICAINE 2% CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8349,8 +8437,16 @@
           <t>4599214518-579-032743271265</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>MEDEMYCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8532,8 +8628,16 @@
           <t>7864148739-999-295290734835</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MEDAFEN 100MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8914,8 +9018,16 @@
           <t>5348277926-630-732544082409</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>MEDICAINE 3% CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9093,8 +9205,16 @@
           <t>0671117792-345-638367374370</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>MEDACIN -T 1% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9276,8 +9396,16 @@
           <t>9811303911-577-021390687790</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>MEDACEF 500MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9459,8 +9587,16 @@
           <t>5334553217-382-337889532053</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MEDACEF 250MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9642,8 +9778,16 @@
           <t>7708307386-691-161472701283</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LOPRAM 20MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10390,8 +10534,16 @@
           <t>3348671860-776-453343969907</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LECITAL 20MG F.C. CAPLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10573,8 +10725,16 @@
           <t>4031916190-521-730780275527</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>LAXOLAC SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10752,8 +10912,16 @@
           <t>7257875410-006-175739832584</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>LAXOLAC SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10935,8 +11103,16 @@
           <t>1640200917-149-879855571747</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>LAXO detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11496,8 +11672,16 @@
           <t>3220237997-141-631326435390</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LASONIL OINT detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11870,8 +12054,16 @@
           <t>1426270267-721-263059614807</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>LENDOMAX 70 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12242,8 +12434,16 @@
           <t>1228641205-773-028028661998</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>LEVSIN TAB 0.125MG detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13360,8 +13560,16 @@
           <t>0043942833-590-729589475756</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LEVITRA 5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13539,8 +13747,16 @@
           <t>3492859131-484-786416187362</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LEVITRA 20MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13718,8 +13934,16 @@
           <t>5145104835-673-150448153729</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LEVITRA 10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -14104,8 +14328,16 @@
           <t>4524853029-420-647986683254</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>LEUKAST 10MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14482,8 +14714,16 @@
           <t>4315156509-090-002125003201</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>LAMISIL ONCE 1% CUTANEOUS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -16927,8 +17167,16 @@
           <t>8237948455-448-773719964037</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>LAMOTRIX 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17110,8 +17358,16 @@
           <t>3191962390-384-974140079830</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LAMOTRIX 25MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17293,8 +17549,16 @@
           <t>2694158116-678-789793986723</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LAMOTRIX 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17480,8 +17744,16 @@
           <t>7663933271-684-030944260733</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>LAPRIL 5 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17663,8 +17935,16 @@
           <t>2921476514-752-596950883491</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>LAPRIL 20MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17846,8 +18126,16 @@
           <t>9565359758-068-822631075178</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>LAPRIL 20 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18590,8 +18878,16 @@
           <t>4872155691-108-671401278957</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>LANTUS 100 I.U - ML VIAL detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Sanofi Aventis Arabia</t>
@@ -18779,8 +19075,16 @@
           <t>8149062174-617-664478287100</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>LANSOMID 30 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/4/file.xlsx
+++ b/product_upload/packages/4/file.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21431,7 +21431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21512,40 +21512,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21625,38 +21630,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>498.9</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-3F7D1F1D7114</t>
         </is>
@@ -21736,38 +21746,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>278.99</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-00F35A0B7D76</t>
         </is>
@@ -21847,38 +21862,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>292.6</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-F1A1352812E2</t>
         </is>
@@ -21958,38 +21978,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>450.74</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-244670323B03</t>
         </is>
@@ -22069,38 +22094,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>318.65</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-FF9A8AEF52B5</t>
         </is>
@@ -22180,38 +22210,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>251.64</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-57F3C1828F9D</t>
         </is>
@@ -22291,38 +22326,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>354.7</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-F9F2683E7EF1</t>
         </is>
@@ -22402,38 +22442,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>383.5</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-84DF185E6DC9</t>
         </is>
@@ -22513,38 +22558,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>73.48</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-425FA6D90F49</t>
         </is>
@@ -22624,38 +22674,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>22.36</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-DDF5EF51C975</t>
         </is>
@@ -22735,38 +22790,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>371.84</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-9FD4932C4772</t>
         </is>
@@ -22846,38 +22906,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>245.32</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-659325A6836A</t>
         </is>
@@ -22957,38 +23022,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>233.96</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-3D3B7B19BF65</t>
         </is>
@@ -23068,38 +23138,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>30.47</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-06120EEE4392</t>
         </is>
@@ -23179,38 +23254,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>96.98999999999999</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-F576F6E6139F</t>
         </is>
@@ -23290,38 +23370,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>449.07</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-7A99AF0205EC</t>
         </is>
@@ -23401,38 +23486,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>371.24</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-D62D199D668C</t>
         </is>
@@ -23512,38 +23602,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.58</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-EC0A541A81CC</t>
         </is>
@@ -23623,38 +23718,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>350.78</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-01130A522299</t>
         </is>
@@ -23734,38 +23834,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>440.67</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-71CC18CFE1F3</t>
         </is>
